--- a/risks.xlsx
+++ b/risks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28CDBF1-E5E9-492D-B47C-F417119F367E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A940BD55-EDD7-43E1-8141-63A683DB3929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="risks" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>אנליסט</t>
   </si>
   <si>
-    <t>חוסר רציפות מפתחת — תנודתיות עומס</t>
-  </si>
-  <si>
     <t>משאבים</t>
   </si>
   <si>
@@ -67,33 +64,18 @@
     <t>30/06/2025</t>
   </si>
   <si>
-    <t>אין מפתחת קבועה בפרויקט, עומס לא צפוי גורם לאי-עמידה בלוחות זמנים</t>
-  </si>
-  <si>
-    <t>שעות לא billable — גירעון כיסוי כספי</t>
-  </si>
-  <si>
     <t>תקציב</t>
   </si>
   <si>
     <t>בטיפול</t>
   </si>
   <si>
-    <t>שעות עבודה שאינן מכוסות על ידי הזמנות עבודה פעילות</t>
-  </si>
-  <si>
-    <t>עיכובים בגלל תלות בעיצוב ואנליזה</t>
-  </si>
-  <si>
     <t>לוח זמנים</t>
   </si>
   <si>
     <t>31/07/2025</t>
   </si>
   <si>
-    <t>בקשות הדורשות עיצוב/אנליזה מעכבות deliverables כי משאבים אלו על פרויקטים אחרים</t>
-  </si>
-  <si>
     <t>אי-עמידה ב-SLA העלאת גרסה חודשית</t>
   </si>
   <si>
@@ -139,18 +121,9 @@
     <t>3 מפתחים על מערכות מרובות במקביל — סיכון לטעויות ועיכובים</t>
   </si>
   <si>
-    <t>רגולציה — עמידה בדדליינים חוקיים</t>
-  </si>
-  <si>
     <t>שינויי רגולציה תכופים מחייבים פיתוח מיידי</t>
   </si>
   <si>
-    <t>תלות גבוהה בי כמנהלת פרויקט יחידה</t>
-  </si>
-  <si>
-    <t>אני הנקודה המרכזית — אין גיבוי למידע ניהולי</t>
-  </si>
-  <si>
     <t>דלק</t>
   </si>
   <si>
@@ -160,9 +133,6 @@
     <t>רק מפתחת אחת מכירה את המערכת מקצה לקצה — סיכון קריטי</t>
   </si>
   <si>
-    <t>עומס לא צפוי — מפתחת עמוקה בפרויקט אחר</t>
-  </si>
-  <si>
     <t>כשמגיעות משימות, המפתחת כבר מחויבת למקום אחר</t>
   </si>
   <si>
@@ -181,9 +151,6 @@
     <t>תלות בממשקי ליבה של הלקוח</t>
   </si>
   <si>
-    <t>שינויים במערכות הליבה של הלקוח עלולים לשבור את המערכת שלנו</t>
-  </si>
-  <si>
     <t>בנק יהב</t>
   </si>
   <si>
@@ -236,6 +203,39 @@
   </si>
   <si>
     <t>פעילות מוגבלת לתחזוקה בלבד — סיכון שהלקוח יצמצם או יסיים</t>
+  </si>
+  <si>
+    <t>חוסר רציפות בפיתוח — תנודתיות עומס</t>
+  </si>
+  <si>
+    <t>אין עבודה רציפה ומלאה בפיתוח בפרויקט, עומס לא צפוי גורם לאי-עמידה בלוחות זמנים</t>
+  </si>
+  <si>
+    <t>שעות שלא ניתנות לחיוב — גירעון כיסוי כספי</t>
+  </si>
+  <si>
+    <t xml:space="preserve">שעות עבודה שאינן מכוסות על ידי ההזמנות הקיימות </t>
+  </si>
+  <si>
+    <t>עיכובים בגלל תלות בעיצוב וניתוח</t>
+  </si>
+  <si>
+    <t>בקשות הדורשות עיצוב/ניתוח מעכבות דליברי כי משאבים אלו על פרויקטים אחרים</t>
+  </si>
+  <si>
+    <t>רגולציה — עמידה בדדליינים חוקתיים</t>
+  </si>
+  <si>
+    <t>הלקוח מצפה לדליברי הרבה יותר מהיר מבעבר</t>
+  </si>
+  <si>
+    <t>הלקוח מצפה לגרסאות לעיתים תכופות יותר עם תכולה גדולה יותר</t>
+  </si>
+  <si>
+    <t>עומס לא צפוי — מפתחת בפרויקט אחר במקביל</t>
+  </si>
+  <si>
+    <t>שינויים במערכות הליבה של הלקוח עלולים להשפיע על המערכת שלנו באופן מהותי וקריטי</t>
   </si>
 </sst>
 </file>
@@ -635,28 +635,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -664,7 +664,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -673,19 +673,19 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -693,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -702,19 +702,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -731,19 +731,19 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -751,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -760,19 +760,19 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -780,7 +780,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -789,27 +789,27 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -818,27 +818,27 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -847,27 +847,27 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -876,27 +876,27 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -905,27 +905,27 @@
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -934,27 +934,27 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
         <v>13</v>
       </c>
-      <c r="H12" t="s">
-        <v>14</v>
-      </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -963,27 +963,27 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -992,27 +992,27 @@
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
         <v>13</v>
       </c>
-      <c r="H14" t="s">
-        <v>14</v>
-      </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -1021,27 +1021,27 @@
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1050,27 +1050,27 @@
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -1079,27 +1079,27 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1108,27 +1108,27 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
         <v>13</v>
       </c>
-      <c r="H18" t="s">
-        <v>14</v>
-      </c>
       <c r="I18" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1137,27 +1137,27 @@
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -1166,27 +1166,27 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="s">
         <v>13</v>
       </c>
-      <c r="H20" t="s">
-        <v>14</v>
-      </c>
       <c r="I20" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1195,27 +1195,27 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -1224,27 +1224,27 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" t="s">
         <v>13</v>
       </c>
-      <c r="H22" t="s">
-        <v>14</v>
-      </c>
       <c r="I22" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -1253,27 +1253,27 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1282,19 +1282,19 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
